--- a/fold_differences_race_stratified_without_vs_with_sunscreen_adjustment.xlsx
+++ b/fold_differences_race_stratified_without_vs_with_sunscreen_adjustment.xlsx
@@ -1,13 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10910"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vynguyen/Dropbox/Mac/Documents/GitHub/weight_perception_bp3/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B7F514-D22D-4F4E-943D-317EB5E83064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="tidy" r:id="rId3" sheetId="1"/>
+    <sheet name="tidy" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">tidy!$A$1:$M$25</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -230,11 +254,10 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -246,7 +269,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
@@ -264,16 +287,330 @@
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="44" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1"/>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -311,7 +648,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -321,25 +658,25 @@
       <c r="C2" t="s">
         <v>42</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>1.477618616344289</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>1.3576289415887497</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>25.122486990550087</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>1.4176237789665194</v>
       </c>
       <c r="H2" t="s">
         <v>43</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>1.3626289415887496</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>1.4726186163442891</v>
       </c>
       <c r="K2" t="s">
@@ -352,7 +689,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -362,26 +699,26 @@
       <c r="C3" t="s">
         <v>42</v>
       </c>
-      <c r="D3" t="n">
-        <v>2.811909300969573</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2.096203188361786</v>
-      </c>
-      <c r="F3" t="n">
+      <c r="D3">
+        <v>2.8119093009695728</v>
+      </c>
+      <c r="E3">
+        <v>2.0962031883617862</v>
+      </c>
+      <c r="F3">
         <v>39.500106998998476</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>2.4540562446656793</v>
       </c>
       <c r="H3" t="s">
         <v>44</v>
       </c>
-      <c r="I3" t="n">
-        <v>2.101203188361786</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.806909300969573</v>
+      <c r="I3">
+        <v>2.1012031883617861</v>
+      </c>
+      <c r="J3">
+        <v>2.8069093009695729</v>
       </c>
       <c r="K3" t="s">
         <v>66</v>
@@ -393,7 +730,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -403,25 +740,25 @@
       <c r="C4" t="s">
         <v>42</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>1.5481971123324216</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>1.3088171292067687</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>43.666771995051135</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>1.4285071207695952</v>
       </c>
       <c r="H4" t="s">
         <v>45</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>1.3138171292067686</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>1.5431971123324217</v>
       </c>
       <c r="K4" t="s">
@@ -434,7 +771,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -444,26 +781,26 @@
       <c r="C5" t="s">
         <v>42</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.8679104265761879</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9278935415589294</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="D5">
+        <v>0.86791042657618789</v>
+      </c>
+      <c r="E5">
+        <v>0.92789354155892945</v>
+      </c>
+      <c r="F5">
         <v>45.410938522970696</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.8979019840675586</v>
+      <c r="G5">
+        <v>0.89790198406755861</v>
       </c>
       <c r="H5" t="s">
         <v>46</v>
       </c>
-      <c r="I5" t="n">
-        <v>0.9228935415589294</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.8729104265761879</v>
+      <c r="I5">
+        <v>0.92289354155892944</v>
+      </c>
+      <c r="J5">
+        <v>0.87291042657618789</v>
       </c>
       <c r="K5" t="s">
         <v>66</v>
@@ -475,7 +812,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -485,25 +822,25 @@
       <c r="C6" t="s">
         <v>42</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>1.4341650400218546</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>1.0179706650216687</v>
       </c>
-      <c r="F6" t="n">
-        <v>95.8608677887183</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="F6">
+        <v>95.860867788718295</v>
+      </c>
+      <c r="G6">
         <v>1.2260678525217616</v>
       </c>
       <c r="H6" t="s">
         <v>47</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>1.0229706650216686</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>1.4291650400218547</v>
       </c>
       <c r="K6" t="s">
@@ -516,7 +853,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -526,17 +863,17 @@
       <c r="C7" t="s">
         <v>42</v>
       </c>
-      <c r="D7" t="n">
-        <v>0.8330030584562306</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="D7">
+        <v>0.83300305845623057</v>
+      </c>
+      <c r="E7">
         <v>1.0815448934929663</v>
       </c>
-      <c r="F7" t="n">
-        <v>148.8301718217957</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.9572739759745985</v>
+      <c r="F7">
+        <v>148.83017182179569</v>
+      </c>
+      <c r="G7">
+        <v>0.95727397597459851</v>
       </c>
       <c r="H7" t="s">
         <v>48</v>
@@ -557,7 +894,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -567,25 +904,25 @@
       <c r="C8" t="s">
         <v>42</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>1.2572328392675745</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>1.2824435177248663</v>
       </c>
-      <c r="F8" t="n">
-        <v>9.80072316158188</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="F8">
+        <v>9.8007231615818799</v>
+      </c>
+      <c r="G8">
         <v>1.2698381784962205</v>
       </c>
       <c r="H8" t="s">
         <v>49</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>1.2774435177248664</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>1.2622328392675743</v>
       </c>
       <c r="K8" t="s">
@@ -598,7 +935,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -608,25 +945,25 @@
       <c r="C9" t="s">
         <v>42</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>1.6052228909670703</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>1.3761846560842523</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>37.843617335233894</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>1.4907037735256612</v>
       </c>
       <c r="H9" t="s">
         <v>50</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>1.3811846560842522</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>1.6002228909670704</v>
       </c>
       <c r="K9" t="s">
@@ -639,7 +976,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -649,25 +986,25 @@
       <c r="C10" t="s">
         <v>42</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>2.4007824744623774</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>1.7263824765220164</v>
       </c>
-      <c r="F10" t="n">
-        <v>48.14451995476291</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="F10">
+        <v>48.144519954762913</v>
+      </c>
+      <c r="G10">
         <v>2.063582475492197</v>
       </c>
       <c r="H10" t="s">
         <v>51</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>1.7313824765220163</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>2.3957824744623775</v>
       </c>
       <c r="K10" t="s">
@@ -680,7 +1017,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -690,25 +1027,25 @@
       <c r="C11" t="s">
         <v>42</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>1.9320349813692677</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>1.2750840855921088</v>
       </c>
-      <c r="F11" t="n">
-        <v>70.48564795411666</v>
-      </c>
-      <c r="G11" t="n">
+      <c r="F11">
+        <v>70.485647954116658</v>
+      </c>
+      <c r="G11">
         <v>1.6035595334806882</v>
       </c>
       <c r="H11" t="s">
         <v>52</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>1.2800840855921087</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>1.9270349813692678</v>
       </c>
       <c r="K11" t="s">
@@ -721,7 +1058,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -731,16 +1068,16 @@
       <c r="C12" t="s">
         <v>42</v>
       </c>
-      <c r="D12" t="n">
-        <v>0.9515353803954981</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="D12">
+        <v>0.95153538039549812</v>
+      </c>
+      <c r="E12">
         <v>1.036487181893488</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>175.2862236230132</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>0.994011281144493</v>
       </c>
       <c r="H12" t="s">
@@ -762,7 +1099,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -772,25 +1109,25 @@
       <c r="C13" t="s">
         <v>42</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>1.1413535754228514</v>
       </c>
-      <c r="E13" t="n">
-        <v>1.597689665213403</v>
-      </c>
-      <c r="F13" t="n">
+      <c r="E13">
+        <v>1.5976896652134029</v>
+      </c>
+      <c r="F13">
         <v>322.8330719088267</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>1.3695216203181273</v>
       </c>
       <c r="H13" t="s">
         <v>54</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>1.592689665213403</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>1.1463535754228513</v>
       </c>
       <c r="K13" t="s">
@@ -803,7 +1140,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -813,25 +1150,25 @@
       <c r="C14" t="s">
         <v>42</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>1.461479441477991</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>1.3582211722510384</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>22.375486304708375</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>1.4098503068645147</v>
       </c>
       <c r="H14" t="s">
         <v>55</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>1.3632211722510383</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>1.4564794414779911</v>
       </c>
       <c r="K14" t="s">
@@ -844,7 +1181,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -854,26 +1191,26 @@
       <c r="C15" t="s">
         <v>42</v>
       </c>
-      <c r="D15" t="n">
-        <v>2.687929621003465</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2.126058426740178</v>
-      </c>
-      <c r="F15" t="n">
+      <c r="D15">
+        <v>2.6879296210034651</v>
+      </c>
+      <c r="E15">
+        <v>2.1260584267401779</v>
+      </c>
+      <c r="F15">
         <v>33.287596074607535</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>2.4069940238718215</v>
       </c>
       <c r="H15" t="s">
         <v>56</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>2.1310584267401778</v>
       </c>
-      <c r="J15" t="n">
-        <v>2.682929621003465</v>
+      <c r="J15">
+        <v>2.6829296210034652</v>
       </c>
       <c r="K15" t="s">
         <v>66</v>
@@ -885,7 +1222,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -895,25 +1232,25 @@
       <c r="C16" t="s">
         <v>42</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>1.4236262890855922</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>1.2633840357661505</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>37.826324155974476</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>1.3435051624258714</v>
       </c>
       <c r="H16" t="s">
         <v>50</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>1.2683840357661504</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>1.4186262890855923</v>
       </c>
       <c r="K16" t="s">
@@ -926,7 +1263,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -936,26 +1273,26 @@
       <c r="C17" t="s">
         <v>42</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.8595169307899088</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.9130012729916505</v>
-      </c>
-      <c r="F17" t="n">
-        <v>38.07173526494949</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.8862591018907796</v>
+      <c r="D17">
+        <v>0.85951693078990876</v>
+      </c>
+      <c r="E17">
+        <v>0.91300127299165046</v>
+      </c>
+      <c r="F17">
+        <v>38.071735264949488</v>
+      </c>
+      <c r="G17">
+        <v>0.88625910189077961</v>
       </c>
       <c r="H17" t="s">
         <v>57</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.9080012729916505</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.8645169307899088</v>
+      <c r="I17">
+        <v>0.90800127299165045</v>
+      </c>
+      <c r="J17">
+        <v>0.86451693078990877</v>
       </c>
       <c r="K17" t="s">
         <v>66</v>
@@ -967,7 +1304,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -977,25 +1314,25 @@
       <c r="C18" t="s">
         <v>42</v>
       </c>
-      <c r="D18" t="n">
-        <v>1.273969770465012</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.9726604668105217</v>
-      </c>
-      <c r="F18" t="n">
+      <c r="D18">
+        <v>1.2739697704650119</v>
+      </c>
+      <c r="E18">
+        <v>0.97266046681052165</v>
+      </c>
+      <c r="F18">
         <v>109.97903277543163</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18">
         <v>1.1233151186377668</v>
       </c>
       <c r="H18" t="s">
         <v>58</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.9776604668105217</v>
-      </c>
-      <c r="J18" t="n">
+      <c r="I18">
+        <v>0.97766046681052166</v>
+      </c>
+      <c r="J18">
         <v>1.268969770465012</v>
       </c>
       <c r="K18" t="s">
@@ -1008,7 +1345,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -1018,16 +1355,16 @@
       <c r="C19" t="s">
         <v>42</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>0.9437728769354734</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>1.1291357276687666</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>329.6680332027118</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>1.03645430230212</v>
       </c>
       <c r="H19" t="s">
@@ -1049,7 +1386,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -1059,25 +1396,25 @@
       <c r="C20" t="s">
         <v>42</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>1.2669907359042298</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>1.2848137253207077</v>
       </c>
-      <c r="F20" t="n">
-        <v>6.675508555050018</v>
-      </c>
-      <c r="G20" t="n">
+      <c r="F20">
+        <v>6.6755085550500182</v>
+      </c>
+      <c r="G20">
         <v>1.2759022306124688</v>
       </c>
       <c r="H20" t="s">
         <v>60</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20">
         <v>1.2798137253207078</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20">
         <v>1.2719907359042297</v>
       </c>
       <c r="K20" t="s">
@@ -1090,7 +1427,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>31</v>
       </c>
@@ -1100,25 +1437,25 @@
       <c r="C21" t="s">
         <v>42</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>1.495376869393745</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>1.3404817224858554</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>31.268142797513796</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>1.4179292959398002</v>
       </c>
       <c r="H21" t="s">
         <v>61</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21">
         <v>1.3454817224858553</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21">
         <v>1.4903768693937451</v>
       </c>
       <c r="K21" t="s">
@@ -1131,7 +1468,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>32</v>
       </c>
@@ -1141,25 +1478,25 @@
       <c r="C22" t="s">
         <v>42</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>2.2719339820857063</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>1.7330180016959122</v>
       </c>
-      <c r="F22" t="n">
-        <v>42.36980755133881</v>
-      </c>
-      <c r="G22" t="n">
+      <c r="F22">
+        <v>42.369807551338809</v>
+      </c>
+      <c r="G22">
         <v>2.002475991890809</v>
       </c>
       <c r="H22" t="s">
         <v>62</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22">
         <v>1.7380180016959121</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22">
         <v>2.2669339820857064</v>
       </c>
       <c r="K22" t="s">
@@ -1172,7 +1509,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -1182,25 +1519,25 @@
       <c r="C23" t="s">
         <v>42</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>1.7775205437130435</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>1.2551536395008136</v>
       </c>
-      <c r="F23" t="n">
-        <v>67.1836787382711</v>
-      </c>
-      <c r="G23" t="n">
+      <c r="F23">
+        <v>67.183678738271098</v>
+      </c>
+      <c r="G23">
         <v>1.5163370916069285</v>
       </c>
       <c r="H23" t="s">
         <v>63</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23">
         <v>1.2601536395008135</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23">
         <v>1.7725205437130436</v>
       </c>
       <c r="K23" t="s">
@@ -1213,7 +1550,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -1223,26 +1560,26 @@
       <c r="C24" t="s">
         <v>42</v>
       </c>
-      <c r="D24" t="n">
-        <v>0.9117279890369663</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.9947010508372414</v>
-      </c>
-      <c r="F24" t="n">
-        <v>93.99702226680016</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.9532145199371038</v>
+      <c r="D24">
+        <v>0.91172798903696628</v>
+      </c>
+      <c r="E24">
+        <v>0.99470105083724136</v>
+      </c>
+      <c r="F24">
+        <v>93.997022266800158</v>
+      </c>
+      <c r="G24">
+        <v>0.95321451993710382</v>
       </c>
       <c r="H24" t="s">
         <v>64</v>
       </c>
-      <c r="I24" t="n">
-        <v>0.9897010508372414</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.9167279890369663</v>
+      <c r="I24">
+        <v>0.98970105083724136</v>
+      </c>
+      <c r="J24">
+        <v>0.91672798903696628</v>
       </c>
       <c r="K24" t="s">
         <v>67</v>
@@ -1254,7 +1591,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
@@ -1264,25 +1601,25 @@
       <c r="C25" t="s">
         <v>42</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>1.1831117305783965</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>1.5752045477072447</v>
       </c>
-      <c r="F25" t="n">
-        <v>214.12763447232</v>
-      </c>
-      <c r="G25" t="n">
+      <c r="F25">
+        <v>214.12763447232001</v>
+      </c>
+      <c r="G25">
         <v>1.3791581391428207</v>
       </c>
       <c r="H25" t="s">
         <v>65</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25">
         <v>1.5702045477072448</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25">
         <v>1.1881117305783964</v>
       </c>
       <c r="K25" t="s">
@@ -1296,6 +1633,18 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <autoFilter ref="A1:M25" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="weighted"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="12">
+      <filters>
+        <filter val="RIDAGEYR + SDDSRVYR + URXUCR + BMXBMI + INDFMPIR"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>